--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245868</v>
+        <v>122245864</v>
       </c>
       <c r="B2" t="n">
-        <v>79228</v>
+        <v>78027</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770433</v>
+        <v>770500</v>
       </c>
       <c r="R2" t="n">
-        <v>7112731</v>
+        <v>7112712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245864</v>
+        <v>122245863</v>
       </c>
       <c r="B3" t="n">
-        <v>78023</v>
+        <v>77575</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245871</v>
+        <v>122245867</v>
       </c>
       <c r="B4" t="n">
-        <v>78673</v>
+        <v>79261</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770632</v>
+        <v>770470</v>
       </c>
       <c r="R4" t="n">
-        <v>7112652</v>
+        <v>7112682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245867</v>
+        <v>122245868</v>
       </c>
       <c r="B5" t="n">
-        <v>79257</v>
+        <v>79232</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770470</v>
+        <v>770433</v>
       </c>
       <c r="R5" t="n">
-        <v>7112682</v>
+        <v>7112731</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245863</v>
+        <v>122245866</v>
       </c>
       <c r="B6" t="n">
-        <v>77571</v>
+        <v>79261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770500</v>
+        <v>770448</v>
       </c>
       <c r="R6" t="n">
-        <v>7112712</v>
+        <v>7112735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245866</v>
+        <v>122245871</v>
       </c>
       <c r="B7" t="n">
-        <v>79257</v>
+        <v>78677</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770448</v>
+        <v>770632</v>
       </c>
       <c r="R7" t="n">
-        <v>7112735</v>
+        <v>7112652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,6 +1289,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245866</v>
+        <v>122245867</v>
       </c>
       <c r="B3" t="n">
         <v>79263</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770448</v>
+        <v>770470</v>
       </c>
       <c r="R3" t="n">
-        <v>7112735</v>
+        <v>7112682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245864</v>
+        <v>122245866</v>
       </c>
       <c r="B5" t="n">
-        <v>78029</v>
+        <v>79263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770500</v>
+        <v>770448</v>
       </c>
       <c r="R5" t="n">
-        <v>7112712</v>
+        <v>7112735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245867</v>
+        <v>122245864</v>
       </c>
       <c r="B7" t="n">
-        <v>79263</v>
+        <v>78029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770470</v>
+        <v>770500</v>
       </c>
       <c r="R7" t="n">
-        <v>7112682</v>
+        <v>7112712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245868</v>
+        <v>122245866</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
+        <v>79264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770433</v>
+        <v>770448</v>
       </c>
       <c r="R2" t="n">
-        <v>7112731</v>
+        <v>7112735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122245867</v>
       </c>
       <c r="B3" t="n">
-        <v>79263</v>
+        <v>79264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245863</v>
+        <v>122245868</v>
       </c>
       <c r="B4" t="n">
-        <v>77577</v>
+        <v>79235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770500</v>
+        <v>770433</v>
       </c>
       <c r="R4" t="n">
-        <v>7112712</v>
+        <v>7112731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245866</v>
+        <v>122245864</v>
       </c>
       <c r="B5" t="n">
-        <v>79263</v>
+        <v>78030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770448</v>
+        <v>770500</v>
       </c>
       <c r="R5" t="n">
-        <v>7112735</v>
+        <v>7112712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245871</v>
+        <v>122245863</v>
       </c>
       <c r="B6" t="n">
-        <v>78679</v>
+        <v>77578</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770632</v>
+        <v>770500</v>
       </c>
       <c r="R6" t="n">
-        <v>7112652</v>
+        <v>7112712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245864</v>
+        <v>122245871</v>
       </c>
       <c r="B7" t="n">
-        <v>78029</v>
+        <v>78680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770500</v>
+        <v>770632</v>
       </c>
       <c r="R7" t="n">
-        <v>7112712</v>
+        <v>7112652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,6 +1289,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245866</v>
+        <v>122245868</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770448</v>
+        <v>770433</v>
       </c>
       <c r="R2" t="n">
-        <v>7112735</v>
+        <v>7112731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245867</v>
+        <v>122245871</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>78680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770470</v>
+        <v>770632</v>
       </c>
       <c r="R3" t="n">
-        <v>7112682</v>
+        <v>7112652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +865,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245868</v>
+        <v>122245867</v>
       </c>
       <c r="B4" t="n">
-        <v>79235</v>
+        <v>79264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770433</v>
+        <v>770470</v>
       </c>
       <c r="R4" t="n">
-        <v>7112731</v>
+        <v>7112682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245864</v>
+        <v>122245863</v>
       </c>
       <c r="B5" t="n">
-        <v>78030</v>
+        <v>77578</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1099,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245863</v>
+        <v>122245864</v>
       </c>
       <c r="B6" t="n">
-        <v>77578</v>
+        <v>78030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245871</v>
+        <v>122245866</v>
       </c>
       <c r="B7" t="n">
-        <v>78680</v>
+        <v>79264</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770632</v>
+        <v>770448</v>
       </c>
       <c r="R7" t="n">
-        <v>7112652</v>
+        <v>7112735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1290,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245868</v>
+        <v>122245864</v>
       </c>
       <c r="B2" t="n">
-        <v>79235</v>
+        <v>78035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770433</v>
+        <v>770500</v>
       </c>
       <c r="R2" t="n">
-        <v>7112731</v>
+        <v>7112712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122245871</v>
       </c>
       <c r="B3" t="n">
-        <v>78680</v>
+        <v>78685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>122245867</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245863</v>
+        <v>122245868</v>
       </c>
       <c r="B5" t="n">
-        <v>77578</v>
+        <v>79240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770500</v>
+        <v>770433</v>
       </c>
       <c r="R5" t="n">
-        <v>7112712</v>
+        <v>7112731</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245864</v>
+        <v>122245866</v>
       </c>
       <c r="B6" t="n">
-        <v>78030</v>
+        <v>79269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770500</v>
+        <v>770448</v>
       </c>
       <c r="R6" t="n">
-        <v>7112712</v>
+        <v>7112735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245866</v>
+        <v>122245863</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>77583</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770448</v>
+        <v>770500</v>
       </c>
       <c r="R7" t="n">
-        <v>7112735</v>
+        <v>7112712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245864</v>
+        <v>122245868</v>
       </c>
       <c r="B2" t="n">
-        <v>78035</v>
+        <v>79240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770500</v>
+        <v>770433</v>
       </c>
       <c r="R2" t="n">
-        <v>7112712</v>
+        <v>7112731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245867</v>
+        <v>122245864</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>78035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770470</v>
+        <v>770500</v>
       </c>
       <c r="R4" t="n">
-        <v>7112682</v>
+        <v>7112712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245868</v>
+        <v>122245866</v>
       </c>
       <c r="B5" t="n">
-        <v>79240</v>
+        <v>79269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770433</v>
+        <v>770448</v>
       </c>
       <c r="R5" t="n">
-        <v>7112731</v>
+        <v>7112735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245866</v>
+        <v>122245867</v>
       </c>
       <c r="B6" t="n">
         <v>79269</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770448</v>
+        <v>770470</v>
       </c>
       <c r="R6" t="n">
-        <v>7112735</v>
+        <v>7112682</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245867</v>
+        <v>122245863</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>77583</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770470</v>
+        <v>770500</v>
       </c>
       <c r="R6" t="n">
-        <v>7112682</v>
+        <v>7112712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245863</v>
+        <v>122245867</v>
       </c>
       <c r="B7" t="n">
-        <v>77583</v>
+        <v>79269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770500</v>
+        <v>770470</v>
       </c>
       <c r="R7" t="n">
-        <v>7112712</v>
+        <v>7112682</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245868</v>
+        <v>122245864</v>
       </c>
       <c r="B2" t="n">
-        <v>79240</v>
+        <v>78036</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
+        <v>6437</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770433</v>
+        <v>770500</v>
       </c>
       <c r="R2" t="n">
-        <v>7112731</v>
+        <v>7112712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245871</v>
+        <v>122245868</v>
       </c>
       <c r="B3" t="n">
-        <v>78685</v>
+        <v>79241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>229821</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770632</v>
+        <v>770433</v>
       </c>
       <c r="R3" t="n">
-        <v>7112652</v>
+        <v>7112731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245864</v>
+        <v>122245867</v>
       </c>
       <c r="B4" t="n">
-        <v>78035</v>
+        <v>79270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +893,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770500</v>
+        <v>770470</v>
       </c>
       <c r="R4" t="n">
-        <v>7112712</v>
+        <v>7112682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245866</v>
+        <v>122245871</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>78686</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +994,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770448</v>
+        <v>770632</v>
       </c>
       <c r="R5" t="n">
-        <v>7112735</v>
+        <v>7112652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1057,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,7 +1083,7 @@
         <v>122245863</v>
       </c>
       <c r="B6" t="n">
-        <v>77583</v>
+        <v>77584</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,11 +1097,6 @@
       </c>
       <c r="E6" t="n">
         <v>6487</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1206,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245867</v>
+        <v>122245866</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>79270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,11 +1199,6 @@
       <c r="E7" t="n">
         <v>6453</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Hertelidea botryosa</t>
@@ -1246,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770470</v>
+        <v>770448</v>
       </c>
       <c r="R7" t="n">
-        <v>7112682</v>
+        <v>7112735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245864</v>
+        <v>122245868</v>
       </c>
       <c r="B2" t="n">
-        <v>78036</v>
+        <v>79245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>229821</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770500</v>
+        <v>770433</v>
       </c>
       <c r="R2" t="n">
-        <v>7112712</v>
+        <v>7112731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245868</v>
+        <v>122245864</v>
       </c>
       <c r="B3" t="n">
-        <v>79241</v>
+        <v>78040</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -792,16 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6437</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770433</v>
+        <v>770500</v>
       </c>
       <c r="R3" t="n">
-        <v>7112731</v>
+        <v>7112712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245867</v>
+        <v>122245863</v>
       </c>
       <c r="B4" t="n">
-        <v>79270</v>
+        <v>77588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -893,16 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6487</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770470</v>
+        <v>770500</v>
       </c>
       <c r="R4" t="n">
-        <v>7112682</v>
+        <v>7112712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245871</v>
+        <v>122245866</v>
       </c>
       <c r="B5" t="n">
-        <v>78686</v>
+        <v>79274</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,16 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770632</v>
+        <v>770448</v>
       </c>
       <c r="R5" t="n">
-        <v>7112652</v>
+        <v>7112735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,7 +1077,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245863</v>
+        <v>122245867</v>
       </c>
       <c r="B6" t="n">
-        <v>77584</v>
+        <v>79274</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1096,16 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770500</v>
+        <v>770470</v>
       </c>
       <c r="R6" t="n">
-        <v>7112712</v>
+        <v>7112682</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245866</v>
+        <v>122245871</v>
       </c>
       <c r="B7" t="n">
-        <v>79270</v>
+        <v>78690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,16 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1216,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770448</v>
+        <v>770632</v>
       </c>
       <c r="R7" t="n">
-        <v>7112735</v>
+        <v>7112652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,6 +1289,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245868</v>
+        <v>122245866</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770433</v>
+        <v>770448</v>
       </c>
       <c r="R2" t="n">
-        <v>7112731</v>
+        <v>7112735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245863</v>
+        <v>122245868</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
+        <v>79245</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770500</v>
+        <v>770433</v>
       </c>
       <c r="R4" t="n">
-        <v>7112712</v>
+        <v>7112731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245866</v>
+        <v>122245871</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>78690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770448</v>
+        <v>770632</v>
       </c>
       <c r="R5" t="n">
-        <v>7112735</v>
+        <v>7112652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1077,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245871</v>
+        <v>122245863</v>
       </c>
       <c r="B7" t="n">
-        <v>78690</v>
+        <v>77588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770632</v>
+        <v>770500</v>
       </c>
       <c r="R7" t="n">
-        <v>7112652</v>
+        <v>7112712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1290,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,6 +1305,131 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122599805</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söravamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>770390</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7112773</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245866</v>
+        <v>122245868</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770448</v>
+        <v>770433</v>
       </c>
       <c r="R2" t="n">
-        <v>7112735</v>
+        <v>7112731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245864</v>
+        <v>122245863</v>
       </c>
       <c r="B3" t="n">
-        <v>78040</v>
+        <v>77588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245868</v>
+        <v>122245871</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>78690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770433</v>
+        <v>770632</v>
       </c>
       <c r="R4" t="n">
-        <v>7112731</v>
+        <v>7112652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245871</v>
+        <v>122245864</v>
       </c>
       <c r="B5" t="n">
-        <v>78690</v>
+        <v>78040</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770632</v>
+        <v>770500</v>
       </c>
       <c r="R5" t="n">
-        <v>7112652</v>
+        <v>7112712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245863</v>
+        <v>122245866</v>
       </c>
       <c r="B7" t="n">
-        <v>77588</v>
+        <v>79274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770500</v>
+        <v>770448</v>
       </c>
       <c r="R7" t="n">
-        <v>7112712</v>
+        <v>7112735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245863</v>
+        <v>122245867</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
+        <v>79274</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770500</v>
+        <v>770470</v>
       </c>
       <c r="R3" t="n">
-        <v>7112712</v>
+        <v>7112682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245871</v>
+        <v>122245864</v>
       </c>
       <c r="B4" t="n">
-        <v>78690</v>
+        <v>78040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770632</v>
+        <v>770500</v>
       </c>
       <c r="R4" t="n">
-        <v>7112652</v>
+        <v>7112712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245864</v>
+        <v>122245871</v>
       </c>
       <c r="B5" t="n">
-        <v>78040</v>
+        <v>78690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770500</v>
+        <v>770632</v>
       </c>
       <c r="R5" t="n">
-        <v>7112712</v>
+        <v>7112652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1077,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245867</v>
+        <v>122245866</v>
       </c>
       <c r="B6" t="n">
         <v>79274</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770470</v>
+        <v>770448</v>
       </c>
       <c r="R6" t="n">
-        <v>7112682</v>
+        <v>7112735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245866</v>
+        <v>122245863</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>77588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770448</v>
+        <v>770500</v>
       </c>
       <c r="R7" t="n">
-        <v>7112735</v>
+        <v>7112712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 38778-2024 artfynd.xlsx
+++ b/artfynd/A 38778-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122245868</v>
+        <v>122245863</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>77588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770433</v>
+        <v>770500</v>
       </c>
       <c r="R2" t="n">
-        <v>7112731</v>
+        <v>7112712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122245867</v>
+        <v>122245864</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>78040</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770470</v>
+        <v>770500</v>
       </c>
       <c r="R3" t="n">
-        <v>7112682</v>
+        <v>7112712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122245864</v>
+        <v>122245867</v>
       </c>
       <c r="B4" t="n">
-        <v>78040</v>
+        <v>79274</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770500</v>
+        <v>770470</v>
       </c>
       <c r="R4" t="n">
-        <v>7112712</v>
+        <v>7112682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122245871</v>
+        <v>122245866</v>
       </c>
       <c r="B5" t="n">
-        <v>78690</v>
+        <v>79274</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770632</v>
+        <v>770448</v>
       </c>
       <c r="R5" t="n">
-        <v>7112652</v>
+        <v>7112735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1077,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122245866</v>
+        <v>122245868</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770448</v>
+        <v>770433</v>
       </c>
       <c r="R6" t="n">
-        <v>7112735</v>
+        <v>7112731</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122245863</v>
+        <v>122245871</v>
       </c>
       <c r="B7" t="n">
-        <v>77588</v>
+        <v>78690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>770500</v>
+        <v>770632</v>
       </c>
       <c r="R7" t="n">
-        <v>7112712</v>
+        <v>7112652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,6 +1289,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
